--- a/Outreach tracker.xlsx
+++ b/Outreach tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -451,240 +451,4800 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Gymdesk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dev Tools</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com</t>
+          <t>https://gymdesk.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Dispo Depot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Fintech</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://stripe.com</t>
+          <t>https://dispo-depot.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>CXAI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>E-commerce</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.shopify.com</t>
+          <t>https://cxapp.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>PCLaw | Time Matters</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Marketing SaaS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.hubspot.com</t>
+          <t>https://pclawtimematters.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slack</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://slack.com</t>
+          <t>https://mashura.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Prosperty</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.zendesk.com</t>
+          <t>https://theprosperty.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>PowerTrain, Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Dev Tools</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com</t>
+          <t>https://powertrain.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>The Learning Network</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Productivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.notion.so</t>
+          <t>https://learning.net</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mailchimp</t>
+          <t>BenchPrep</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Marketing SaaS</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://mailchimp.com</t>
+          <t>https://benchprep.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>RealtyAds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com</t>
+          <t>https://realtyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thread HCM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://threadhcm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Leapsome</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://leapsome.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Payfluence HCM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://payfluencehcm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AllianceHCM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://alliancehcm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VieCure</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://viecure.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VITech</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://vitechteam.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sunwave Health</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://lightningstep.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BizLibrary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://bizlibrary.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Disperse</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://disperse.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PetScreening</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://petscreening.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RET Ventures</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://ret.vc</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OnCourse Learning</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://oncourselearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Core Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://coresolutionsinc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TechChange</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://techchange.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CypherWorx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://cypherworx.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mursion</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://mursion.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Avanti Software Inc.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://avanti.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CiiRUS Inc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://ciirus.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FRONTSTEPS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://frontsteps.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Amplifire AI Learning</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://amplifire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Royal Health Inc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://royalemr.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PayNW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://paynw.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Inbox Health</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://inboxhealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Smokeball - Legal Software</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://smokeball.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WealthCounsel, LLC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://wealthcounsel.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tailorbird</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://tailorbird.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Crystal Practice Management</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://crystalpm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gainesville State College</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://acalog.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Fastbreak AI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://fastbreak.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Leonardo247</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://leonardo247.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Patagonia Health</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://patagoniahealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Pathstream</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://pathstream.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Coursedog</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://coursedog.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Populi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://populi.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ethos</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://ethossystems.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cherre</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://cherre.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Encoda</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://encoda.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IHRDC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://ihrdc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RevenueWell</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://revenuewell.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Foxen</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://foxen.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KnowFully Learning Group</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://knowfully.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ORIL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://oril.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Digitail</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://digitail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PermitFlow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://permitflow.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GovWell</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://govwell.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BoomerangFX</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://boomerangfx.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PriceHubble</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://pricehubble.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Revela</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://revela.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MicroPower</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://micropower.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dyverse</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://dyverse.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Rexera (A RealPage Company)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://rexera.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Obligo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://obligo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Greenshades Software</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://greenshades.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NCTI, Inc.</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://ncti.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Billee Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://billee.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mappedin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://mappedin.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SuiteSpot</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://suitespot.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://joindaisy.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IronCircle</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://ironcircle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Compro Technologies</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://comprotechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HouseAmp</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://houseamp.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nantum AI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://nantum.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Livly</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://livly.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Wodify</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://wodify.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Setpoint</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://setpoint.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cortex Building Intelligence</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://cortexintel.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Flylane</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://flylane.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fyxt</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://fyxt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://cwcapital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CERTIFY Health</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://certifyhealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Point and Click Solutions</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://pointandclicksolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MedEvolve, LLC</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://medevolve.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Radix</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://radix.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EdCast by Cornerstone</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://edcast.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LCvista</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://lcvista.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Giraffe360</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://giraffe360.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Buildout</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://buildout.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Forj</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://forj.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EnSoftek</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://ensoftek.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Capterra</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://capterra.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Newton</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://joinnewton.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>medent</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://medent.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Carson</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://carson.live</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Assembly Software</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://assemblysoftware.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Aiwyn</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://aiwyn.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>RMS</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://rmscloud.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Rentsync</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://rentsync.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BibliU</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://bibliu.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Utility Profit</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://utilityprofit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://eve.legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dealpath</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://dealpath.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HqO</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://hqo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Enterprise Health</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://enterprisehealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Beagle</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://joinbeagle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gold Group Enterprises</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://gold-group.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1GEN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://1gen.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Bluedrop ISM</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://bluedropism.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Echo360</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://echo360.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cadmium</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://gocadmium.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Nutiliti</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://nutiliti.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>HelloSpoke</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://hellospoke.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Collectly</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://collectly.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Magellan Financial &amp; Insurance Services, Inc.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://partnerwithmagellan.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>iCEV</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://icevonline.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Vantage Learning</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://vantagelearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PMG Learning</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://pmglearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Associa Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://associamidatlantic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://getbridge.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Growth99</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://growth99.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Brivity</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://brivity.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Centerbase</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://centerbase.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Autosoft DMS</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://autosoftdms.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Trainual</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://trainual.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>iPerformX</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://iperformx.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TeachTown</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://teachtown.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EngageRM</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://engagerm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Archy</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://archy.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jinso Labs</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://jinso.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HR4 Ltd</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://hr4.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>uPerform</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://uperform.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Beable Education</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://beable.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ManageAmerica | Property Management Software</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://manageamerica.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SwiftConnect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://swiftconnect.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Mediafly</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://mediafly.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Unboxed Training &amp; Technology</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://unboxedtechnology.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Owl Practice Suite</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://owlpracticesuite.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ProfitSolv</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://profitsolv.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Venn</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://venn.city</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Turno</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://turno.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Orijin</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://orijin.works</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Practice Better</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://practicebetter.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Intellum</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://intellum.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Fortress OS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://fortresstech.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Valant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://valant.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Xeal</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://xealenergy.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>InScribe</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://inscribeapp.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>EasyLlama</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://easyllama.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SiteCompli��</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://sitecompli.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PNI���HCM</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://pnihcm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Aimsio | Field Service Management Software</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://aimsio.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Valor Capital Group</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://valorcapitalgroup.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>R-Zero</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://rzero.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Learneo</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://learneo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://yoodli.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PatientNow</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://patientnow.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Hostfully</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://hostfully.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tutero</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://tutero.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CBT Nuggets</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://cbtnuggets.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>LIKK Technologies</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://likktechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Software of Excellence</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://softwareofexcellence.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Hawkes Learning</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://hawkeslearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Amenify</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://amenify.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RentVision</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://rentvision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Re-Leased</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://re-leased.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DashQ</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://dashq.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Tribe Capital</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://tribecap.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Anewgo</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://anewgo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://rex.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Stayntouch</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://stayntouch.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Agora</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://agorareal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>JMI Equity</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://jmi.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Total CSR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://totalcsr.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Trainning Education</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://trainning.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Prositions, Inc.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://prositions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Education Advanced</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://educationadvanced.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Functionize</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://functionize.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Practice by Numbers</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://practicenumbers.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Cott Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://cottsystems.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Kairos</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://kairoswater.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Chorus Innovations</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://joinchorus.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Operto</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://operto.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AppWork</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://appworkco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ethena</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://goethena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Mangomint</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://mangomint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Altrio</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://altrio.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Cardinality-ai</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://cardyai.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Dosen</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://dosen.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Tithe.ly</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://tithe.ly</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ValueCheck</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://valuecheck.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Canopy Analytics</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://canopyanalytics.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Moofwd, Inc.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://moofwd.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Plumm</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://heyplumm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BuildWitt</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://buildwitt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Derivita</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://derivita.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FlatWorld</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://flatworld.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>NoRedInk</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://noredink.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CE21</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://ce21.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Thought Industries</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://thoughtindustries.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Stack Sports</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://stacksports.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>MyTime</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://mytime.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>MaxAssist��</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://maxassist.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Meridian Knowledge Solutions</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://meridianks.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Osmind</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://osmind.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Genea</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://getgenea.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Pereview Software</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://pereviewsoftware.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Zenarate</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://zenarate.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SmartAdvocate LLC</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://smartadvocate.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Habyt</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://habyt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>OSI GROUP - GROUPE SOI</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://opto.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Tirios</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://tirios.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sycle</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://sycle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PHIMED Technologies</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://phimed.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Jones Software</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://getjones.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Funnel Leasing</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://funnelleasing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Bardavon</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://bardavon.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>NexTrust, Inc.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://billflash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Eagle Point Software</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://eaglepoint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Spekit ����</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://spekit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>BuzzBoard</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://buzzboard.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>pMD</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://pmd.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Schoox</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://schoox.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Comevo, Inc.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://comevo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>StartCHURCH</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://startchurch.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Qount</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://qount.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Pay Ready</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://payready.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CoVet</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://co.vet</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Marker Learning</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://markerlearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Labster</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://labster.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PointOne</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://pointone.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Ticmas</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://ticmas.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Unlimited Systems</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://unlimitedsystems.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>LineLeader by ChildcareCRM</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://lineleader.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Orbital</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://orbital.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ChurnZero</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://churnzero.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Esusu</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://esusurent.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SETWorks</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://set-works.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>GreenLite</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://greenlite.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://dispatch.me</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Dazos</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://dazos.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MediMobile</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://medimobile.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Vertican Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://vertican.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Learning Explorer</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://learningexplorer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Knowledge Coop</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://knowledgecoop.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>iCareManager</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://icaremanager.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Kognity</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://kognity.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>BVS Performance Solutions</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://bvs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Miaplaza, Inc.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://miaplaza.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ICANotes LLC</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://icanotes.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SmartSimple Software</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://smartsimple.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Knock</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://knock.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Prophia</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://prophia.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Motivity</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://motivity.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Carebility</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://carebility.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>GoRout</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://gorout.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Blumberg Capital</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://blumbergcapital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Fusion Health</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://fusionehr.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Civitas Learning</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://civitaslearning.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Sopheon is now Wellspring</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://wellspring.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Yosi Health</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://yosi.health</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>OneApp</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://oneapp.rentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Continued</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://continued.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Wonderschool</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://wonderschool.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Vubiz</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://vubiz.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Newzip</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://newzip.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Cantata Health Solutions</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://cantatahealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ApartmentIQ</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://apartmentiq.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>URBN Playground</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://urbnplayground.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CareAbout Health</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://careabout.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Nymbl Systems</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://nymblsystems.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>NAI Excel - Texas</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://excelcres.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Local Logic</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://locallogic.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ManageGo</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://managego.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>PeopleGrove</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://peoplegrove.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://exec.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Transact Capital Partners, LLC</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://transactcapital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Spherexx.com</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://spherexx.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Hyly.AI</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://hyly.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Atomi</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://getatomi.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Workiz</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://workiz.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>RentSpree</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://rentspree.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Archipelago</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://onarchipelago.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Intiveo</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://intiveo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Stemble Learning Inc.</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://stemble.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://cardioone.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Clearwave Corporation</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://clearwaveinc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Pi��ata Rent</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://pinata.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Volition Capital</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://volitioncapital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Empyra</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://empyra.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>WRS Health</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://wrshealth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Otto</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://otto.vet</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Emtrain</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://emtrain.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>A2Z</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://a2zsync.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Luma Health</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://lumahealth.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1VALET</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://1valet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Genio</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://genio.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Position Imaging</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://position-imaging.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://balcony.technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>DoorLoop</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://doorloop.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Sigmund Software</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://sigmundsoftware.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MoveDocs</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://movedocs.com</t>
         </is>
       </c>
     </row>
